--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_30.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_30.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>ReactionTime</t>
+          <t>RiskTaker?</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Perfectionism</t>
+          <t>HoursSleep</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.3537920962642259</v>
+        <v>-1.731094447707534</v>
       </c>
       <c r="C2">
-        <v>-1.02496613395825</v>
+        <v>-0.8858905848159222</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.7353896825966466</v>
+        <v>-0.307108335465547</v>
       </c>
       <c r="C3">
-        <v>-0.1638203423133776</v>
+        <v>1.042092795294719</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.8914177800533355</v>
+        <v>-0.1635418518095597</v>
       </c>
       <c r="C4">
-        <v>-0.4675274373131808</v>
+        <v>0.8072311507015167</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.140671634941326</v>
+        <v>0.3913843175217379</v>
       </c>
       <c r="C5">
-        <v>0.8134590966404586</v>
+        <v>-2.081695673598709</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.4760662130887359</v>
+        <v>0.1815166574209938</v>
       </c>
       <c r="C6">
-        <v>-0.3328191173894998</v>
+        <v>-0.5361778652055686</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.5169579135184491</v>
+        <v>-0.3087295194389152</v>
       </c>
       <c r="C7">
-        <v>0.6961529545461964</v>
+        <v>0.3392046267957903</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>1.058202305531883</v>
+        <v>0.276582091262948</v>
       </c>
       <c r="C8">
-        <v>-0.4831924694491291</v>
+        <v>2.294664633380933</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.632249154154307</v>
+        <v>-1.264089498174407</v>
       </c>
       <c r="C9">
-        <v>0.4603024570236377</v>
+        <v>-1.422234632578148</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>1.255704993343888</v>
+        <v>1.696042231983307</v>
       </c>
       <c r="C10">
-        <v>0.149850260192665</v>
+        <v>-0.3858107681054922</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.3655534836462111</v>
+        <v>0.1584892158781887</v>
       </c>
       <c r="C11">
-        <v>-0.6373490293058914</v>
+        <v>-0.3086340216115266</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>-0.7021966181257765</v>
+        <v>-0.9006265967159366</v>
       </c>
       <c r="C12">
-        <v>1.150491648569564</v>
+        <v>0.3768886772128293</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>1.396057540196364</v>
+        <v>1.194078991944561</v>
       </c>
       <c r="C13">
-        <v>-1.195167424599503</v>
+        <v>0.3804749369950918</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>-0.7541342569991352</v>
+        <v>0.9858527708608169</v>
       </c>
       <c r="C14">
-        <v>1.057552850936814</v>
+        <v>-0.8060387352753301</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.01199462492412395</v>
+        <v>0.9781086000611013</v>
       </c>
       <c r="C15">
-        <v>-0.7308794172212306</v>
+        <v>-0.149841629304759</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.1057593570666265</v>
+        <v>0.844749457794889</v>
       </c>
       <c r="C16">
-        <v>-2.411488398157332</v>
+        <v>0.1968093124349391</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.8721782951660302</v>
+        <v>0.4114005583670921</v>
       </c>
       <c r="C17">
-        <v>1.31715286619333</v>
+        <v>-0.05854427188942518</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>-0.5591744854571012</v>
+        <v>0.3515202208229936</v>
       </c>
       <c r="C18">
-        <v>0.1100703146457708</v>
+        <v>1.062574799522221</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>1.411188643738582</v>
+        <v>-1.192836314212762</v>
       </c>
       <c r="C19">
-        <v>-0.6909588404978277</v>
+        <v>-0.9787273515409042</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>-0.2991534912916489</v>
+        <v>-0.2810451266295804</v>
       </c>
       <c r="C20">
-        <v>0.8766701511774104</v>
+        <v>-0.09789082378097648</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.07370065736406319</v>
+        <v>0.2743435186383069</v>
       </c>
       <c r="C21">
-        <v>-0.2365892480188706</v>
+        <v>0.7131876375075235</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>1.085599790564006</v>
+        <v>-0.4957734716741676</v>
       </c>
       <c r="C22">
-        <v>1.083310900872292</v>
+        <v>0.02478944306730982</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>-0.8397781083946351</v>
+        <v>1.165150762395188</v>
       </c>
       <c r="C23">
-        <v>0.5812450274338119</v>
+        <v>1.61897199494035</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>0.9610117432755012</v>
+        <v>0.3442913105654051</v>
       </c>
       <c r="C24">
-        <v>-0.8015792900228846</v>
+        <v>-0.4168200545846871</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>-0.5569461047207774</v>
+        <v>1.146525090914432</v>
       </c>
       <c r="C25">
-        <v>1.394900283477273</v>
+        <v>2.542183190641399</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.652776212893329</v>
+        <v>1.676253535493334</v>
       </c>
       <c r="C26">
-        <v>-0.6403571764871914</v>
+        <v>-0.5612981964721266</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.6593484626418114</v>
+        <v>0.8405249125019274</v>
       </c>
       <c r="C27">
-        <v>-1.37960633161892</v>
+        <v>-1.168797666873082</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.165184970754351</v>
+        <v>0.3108045970962559</v>
       </c>
       <c r="C28">
-        <v>-1.229298181864571</v>
+        <v>1.059856096502784</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>-1.739345896552283</v>
+        <v>-0.5338522249756137</v>
       </c>
       <c r="C29">
-        <v>0.8733124813538882</v>
+        <v>-0.4519897702703653</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>-1.438038539516864</v>
+        <v>-0.9882393720521084</v>
       </c>
       <c r="C30">
-        <v>0.828784300031891</v>
+        <v>-1.348811999130361</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>-1.738318127930139</v>
+        <v>-0.5425624919806228</v>
       </c>
       <c r="C31">
-        <v>0.6549696452234419</v>
+        <v>1.577431927257851</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>2.438112885508091</v>
+        <v>0.4952274051470748</v>
       </c>
       <c r="C32">
-        <v>-1.643947171461378</v>
+        <v>-0.2883947066577336</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>-0.009094967241068577</v>
+        <v>0.7138280781693735</v>
       </c>
       <c r="C33">
-        <v>-1.19866805496887</v>
+        <v>0.589735621680434</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.3298391700344215</v>
+        <v>0.8008811595112546</v>
       </c>
       <c r="C34">
-        <v>-0.4856572137478447</v>
+        <v>0.2423066895068505</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>-0.3833426881759009</v>
+        <v>0.9437760552110439</v>
       </c>
       <c r="C35">
-        <v>-1.634305945321639</v>
+        <v>0.7452256530441568</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>-0.1557592075340038</v>
+        <v>-0.401488810430767</v>
       </c>
       <c r="C36">
-        <v>0.3806089682360464</v>
+        <v>-0.8583191062422799</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>-0.9546964446698722</v>
+        <v>-0.08586572366400409</v>
       </c>
       <c r="C37">
-        <v>-1.479743425745664</v>
+        <v>0.1809069156726182</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>1.470162849295352</v>
+        <v>0.1730151083956953</v>
       </c>
       <c r="C38">
-        <v>0.2512392538781193</v>
+        <v>2.418550052401237</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>-0.3233185693726788</v>
+        <v>-0.5905478374197659</v>
       </c>
       <c r="C39">
-        <v>1.325024710706888</v>
+        <v>-0.8671919996649775</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>-0.1826539168215447</v>
+        <v>1.502597228103144</v>
       </c>
       <c r="C40">
-        <v>0.164286893363249</v>
+        <v>-0.7957615046826877</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>-0.7335707858533651</v>
+        <v>0.4531794247262489</v>
       </c>
       <c r="C41">
-        <v>-0.4203635568045819</v>
+        <v>1.131136681574256</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>0.5260730303469797</v>
+        <v>0.3922737027241699</v>
       </c>
       <c r="C42">
-        <v>-1.417719273115521</v>
+        <v>1.273889393302399</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>1.37824260746162</v>
+        <v>-1.241698053744129</v>
       </c>
       <c r="C43">
-        <v>-0.9262010286310187</v>
+        <v>0.2844214368128852</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>0.4472473643339678</v>
+        <v>1.123133915200488</v>
       </c>
       <c r="C44">
-        <v>1.634483285431219</v>
+        <v>0.3273772901189509</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>-0.6401334987447646</v>
+        <v>2.344689700262322</v>
       </c>
       <c r="C45">
-        <v>-0.87375804761287</v>
+        <v>1.561411588519234</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>1.171485342246858</v>
+        <v>1.380927436877317</v>
       </c>
       <c r="C46">
-        <v>-0.8560687253164264</v>
+        <v>1.584740699435646</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>-1.465431383941785</v>
+        <v>-1.521587771787942</v>
       </c>
       <c r="C47">
-        <v>0.1777005981724339</v>
+        <v>-0.1187266763208469</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>0.452259484455705</v>
+        <v>-0.07840997956481201</v>
       </c>
       <c r="C48">
-        <v>0.2779472007058391</v>
+        <v>0.8122830571842823</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>0.141820792786388</v>
+        <v>-0.5228414630055551</v>
       </c>
       <c r="C49">
-        <v>-1.126195590132235</v>
+        <v>1.295458246217057</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>1.034494816296827</v>
+        <v>-1.113317100391351</v>
       </c>
       <c r="C50">
-        <v>0.1821940248523755</v>
+        <v>-0.5682340195256051</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>-0.8355121920253684</v>
+        <v>-0.547950091286359</v>
       </c>
       <c r="C51">
-        <v>0.5324441299632737</v>
+        <v>0.009759583733879945</v>
       </c>
     </row>
     <row r="52">
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="B52">
-        <v>-1.075486242657535</v>
+        <v>0.8791164551907078</v>
       </c>
       <c r="C52">
-        <v>-0.1049080124495125</v>
+        <v>0.05348106492402271</v>
       </c>
     </row>
     <row r="53">
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="B53">
-        <v>-0.3482056874261845</v>
+        <v>-1.434037995703733</v>
       </c>
       <c r="C53">
-        <v>0.5866865431250632</v>
+        <v>-0.3053194842335933</v>
       </c>
     </row>
     <row r="54">
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="B54">
-        <v>-0.1133789763629876</v>
+        <v>-0.669763071509108</v>
       </c>
       <c r="C54">
-        <v>-0.002915666778530328</v>
+        <v>-0.4330413058872747</v>
       </c>
     </row>
     <row r="55">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="B55">
-        <v>-0.4723080069439869</v>
+        <v>-0.07402717861067426</v>
       </c>
       <c r="C55">
-        <v>0.7705912830019455</v>
+        <v>0.05773574593884051</v>
       </c>
     </row>
     <row r="56">
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="B56">
-        <v>-0.5888900435868959</v>
+        <v>1.539429822087819</v>
       </c>
       <c r="C56">
-        <v>0.6202088560023633</v>
+        <v>1.450668760006621</v>
       </c>
     </row>
     <row r="57">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="B57">
-        <v>1.140953970674475</v>
+        <v>-1.796261985875445</v>
       </c>
       <c r="C57">
-        <v>-1.127789644964601</v>
+        <v>-0.2115074887724062</v>
       </c>
     </row>
     <row r="58">
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="B58">
-        <v>-0.9365393739126453</v>
+        <v>1.115531381672824</v>
       </c>
       <c r="C58">
-        <v>-0.4027125041063828</v>
+        <v>1.383894506503674</v>
       </c>
     </row>
     <row r="59">
@@ -1119,10 +1119,10 @@
         </is>
       </c>
       <c r="B59">
-        <v>-0.02936283014597218</v>
+        <v>1.486442256720993</v>
       </c>
       <c r="C59">
-        <v>1.877363471676754</v>
+        <v>-1.475928547800788</v>
       </c>
     </row>
     <row r="60">
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="B60">
-        <v>-0.7418502884608618</v>
+        <v>0.8220928739412405</v>
       </c>
       <c r="C60">
-        <v>-0.1255244725158032</v>
+        <v>0.6012219968475994</v>
       </c>
     </row>
     <row r="61">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="B61">
-        <v>-0.7652162817837742</v>
+        <v>0.1394192584626537</v>
       </c>
       <c r="C61">
-        <v>-0.4365922300065773</v>
+        <v>-0.05365751995855341</v>
       </c>
     </row>
     <row r="62">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="B62">
-        <v>-0.2757522527162367</v>
+        <v>0.8255422433330097</v>
       </c>
       <c r="C62">
-        <v>0.9035210044499062</v>
+        <v>-0.7362765438071889</v>
       </c>
     </row>
     <row r="63">
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="B63">
-        <v>1.743017926479239</v>
+        <v>-0.230664310230725</v>
       </c>
       <c r="C63">
-        <v>-1.185726027595665</v>
+        <v>-0.5525044337263585</v>
       </c>
     </row>
     <row r="64">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="B64">
-        <v>0.8377934337852435</v>
+        <v>0.3673974835985602</v>
       </c>
       <c r="C64">
-        <v>-0.309227157480545</v>
+        <v>-0.02210492599808037</v>
       </c>
     </row>
     <row r="65">
@@ -1197,10 +1197,10 @@
         </is>
       </c>
       <c r="B65">
-        <v>-0.4687373747788255</v>
+        <v>0.3446158827426727</v>
       </c>
       <c r="C65">
-        <v>-1.281922883243536</v>
+        <v>-0.3159473436635403</v>
       </c>
     </row>
     <row r="66">
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="B66">
-        <v>-1.095217954386453</v>
+        <v>0.6470951003712264</v>
       </c>
       <c r="C66">
-        <v>0.4646571767602098</v>
+        <v>0.1946008775489252</v>
       </c>
     </row>
     <row r="67">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="B67">
-        <v>0.1064675506571522</v>
+        <v>-0.7780460731631539</v>
       </c>
       <c r="C67">
-        <v>0.5669037191042472</v>
+        <v>0.8204108598986575</v>
       </c>
     </row>
     <row r="68">
@@ -1236,10 +1236,10 @@
         </is>
       </c>
       <c r="B68">
-        <v>1.855200521458606</v>
+        <v>-1.248211959193573</v>
       </c>
       <c r="C68">
-        <v>-1.413574236692469</v>
+        <v>-0.9414631037855611</v>
       </c>
     </row>
     <row r="69">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="B69">
-        <v>0.2742707615631455</v>
+        <v>0.7312269622788549</v>
       </c>
       <c r="C69">
-        <v>-0.01145329625638986</v>
+        <v>-0.2846127359610818</v>
       </c>
     </row>
     <row r="70">
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="B70">
-        <v>0.7300185541613015</v>
+        <v>0.8075316330494214</v>
       </c>
       <c r="C70">
-        <v>-0.1307314331331429</v>
+        <v>1.931358848791207</v>
       </c>
     </row>
     <row r="71">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="B71">
-        <v>0.783901712760756</v>
+        <v>1.421879738412679</v>
       </c>
       <c r="C71">
-        <v>-0.5894346940734493</v>
+        <v>-0.660858594152821</v>
       </c>
     </row>
     <row r="72">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="B72">
-        <v>-1.589316071186757</v>
+        <v>0.3904838894098749</v>
       </c>
       <c r="C72">
-        <v>-0.8599741524403594</v>
+        <v>-0.7234932305576973</v>
       </c>
     </row>
     <row r="73">
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="B73">
-        <v>-0.720809297161643</v>
+        <v>0.09650609801856304</v>
       </c>
       <c r="C73">
-        <v>1.017037935594736</v>
+        <v>-1.345383097781357</v>
       </c>
     </row>
     <row r="74">
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="B74">
-        <v>-0.9875110577403232</v>
+        <v>0.4085256292198687</v>
       </c>
       <c r="C74">
-        <v>0.3697438435921196</v>
+        <v>0.223443554343818</v>
       </c>
     </row>
     <row r="75">
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="B75">
-        <v>-2.005440048779378</v>
+        <v>0.5115720121990436</v>
       </c>
       <c r="C75">
-        <v>1.453242030058016</v>
+        <v>1.532946708744786</v>
       </c>
     </row>
     <row r="76">
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="B76">
-        <v>-0.3285938147276084</v>
+        <v>0.1021841014273536</v>
       </c>
       <c r="C76">
-        <v>0.7464732119440518</v>
+        <v>0.8923153323622188</v>
       </c>
     </row>
     <row r="77">
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="B77">
-        <v>1.541532150533605</v>
+        <v>0.2912005230604777</v>
       </c>
       <c r="C77">
-        <v>-0.6760844339917491</v>
+        <v>0.8413430434779018</v>
       </c>
     </row>
     <row r="78">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="B78">
-        <v>1.127366188337361</v>
+        <v>0.2510641571485658</v>
       </c>
       <c r="C78">
-        <v>-0.4049425345451939</v>
+        <v>1.103689308284375</v>
       </c>
     </row>
     <row r="79">
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B79">
-        <v>0.2285808543857219</v>
+        <v>2.084368332891469</v>
       </c>
       <c r="C79">
-        <v>0.1120805795846664</v>
+        <v>0.1999597658338164</v>
       </c>
     </row>
     <row r="80">
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="B80">
-        <v>0.6393051665964543</v>
+        <v>-1.663488474157285</v>
       </c>
       <c r="C80">
-        <v>-1.019818540744514</v>
+        <v>-1.147635030739725</v>
       </c>
     </row>
     <row r="81">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="B81">
-        <v>1.935703492012839</v>
+        <v>1.183416382973645</v>
       </c>
       <c r="C81">
-        <v>-1.184397052691095</v>
+        <v>0.823649931436681</v>
       </c>
     </row>
     <row r="82">
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="B82">
-        <v>-0.4233154654065183</v>
+        <v>1.920008011589203</v>
       </c>
       <c r="C82">
-        <v>-0.6299421069634941</v>
+        <v>1.260996528811411</v>
       </c>
     </row>
     <row r="83">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="B83">
-        <v>-1.653583669776296</v>
+        <v>1.504101591760906</v>
       </c>
       <c r="C83">
-        <v>0.3225515647255576</v>
+        <v>1.725950757451275</v>
       </c>
     </row>
     <row r="84">
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="B84">
-        <v>0.6868459071420312</v>
+        <v>0.404047342143927</v>
       </c>
       <c r="C84">
-        <v>-1.175301720989254</v>
+        <v>1.146526123246967</v>
       </c>
     </row>
     <row r="85">
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="B85">
-        <v>-0.4509348945305127</v>
+        <v>0.8455525093680468</v>
       </c>
       <c r="C85">
-        <v>-0.02912567986300729</v>
+        <v>1.273112028323688</v>
       </c>
     </row>
     <row r="86">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="B86">
-        <v>2.040366294576501</v>
+        <v>-0.6740279192726334</v>
       </c>
       <c r="C86">
-        <v>-1.361480713928964</v>
+        <v>-1.143468365362473</v>
       </c>
     </row>
     <row r="87">
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="B87">
-        <v>-0.5349541606934648</v>
+        <v>0.1206088930522122</v>
       </c>
       <c r="C87">
-        <v>1.470806902647136</v>
+        <v>0.1903993671009031</v>
       </c>
     </row>
     <row r="88">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="B88">
-        <v>-1.619049714863841</v>
+        <v>-0.5743362126966918</v>
       </c>
       <c r="C88">
-        <v>1.052630190764562</v>
+        <v>0.7300722431053581</v>
       </c>
     </row>
     <row r="89">
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="B89">
-        <v>-0.4387394607996163</v>
+        <v>0.2342458515108278</v>
       </c>
       <c r="C89">
-        <v>0.7161100981881887</v>
+        <v>0.4193151383382855</v>
       </c>
     </row>
     <row r="90">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="B90">
-        <v>0.193176823428224</v>
+        <v>0.2972471213783993</v>
       </c>
       <c r="C90">
-        <v>-0.8289372373393744</v>
+        <v>0.2666902561519107</v>
       </c>
     </row>
     <row r="91">
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="B91">
-        <v>0.111621503574056</v>
+        <v>0.9873914105411042</v>
       </c>
       <c r="C91">
-        <v>1.71923417217117</v>
+        <v>0.265248001128112</v>
       </c>
     </row>
     <row r="92">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="B92">
-        <v>0.9990811036626674</v>
+        <v>-0.2383736890325727</v>
       </c>
       <c r="C92">
-        <v>0.681004287330141</v>
+        <v>0.9251178460023926</v>
       </c>
     </row>
     <row r="93">
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="B93">
-        <v>-0.8303970995439396</v>
+        <v>-0.6143234123739372</v>
       </c>
       <c r="C93">
-        <v>-0.4288444847902538</v>
+        <v>-0.5305929379685622</v>
       </c>
     </row>
     <row r="94">
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="B94">
-        <v>0.7201831201665509</v>
+        <v>1.368732044538979</v>
       </c>
       <c r="C94">
-        <v>-0.1144253820775008</v>
+        <v>1.107584603560588</v>
       </c>
     </row>
     <row r="95">
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="B95">
-        <v>1.510550689723525</v>
+        <v>0.4158699779868167</v>
       </c>
       <c r="C95">
-        <v>0.6733780601206787</v>
+        <v>-0.3106989277371462</v>
       </c>
     </row>
     <row r="96">
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="B96">
-        <v>1.381385964650585</v>
+        <v>1.523441584619626</v>
       </c>
       <c r="C96">
-        <v>-1.191369765467562</v>
+        <v>-0.05717386757373522</v>
       </c>
     </row>
     <row r="97">
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="B97">
-        <v>-0.3820018272113946</v>
+        <v>-1.008106407241413</v>
       </c>
       <c r="C97">
-        <v>1.672034423300145</v>
+        <v>-0.05739140607887877</v>
       </c>
     </row>
     <row r="98">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="B98">
-        <v>1.319569672345865</v>
+        <v>1.637107270138006</v>
       </c>
       <c r="C98">
-        <v>1.028790824451794</v>
+        <v>1.126299484355572</v>
       </c>
     </row>
     <row r="99">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="B99">
-        <v>-0.3346569423650054</v>
+        <v>0.08516280533191728</v>
       </c>
       <c r="C99">
-        <v>1.260765938887899</v>
+        <v>0.1145807636499681</v>
       </c>
     </row>
     <row r="100">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="B100">
-        <v>0.2717732558948839</v>
+        <v>1.14183147551476</v>
       </c>
       <c r="C100">
-        <v>0.363390749950921</v>
+        <v>-0.1558469045050728</v>
       </c>
     </row>
     <row r="101">
@@ -1665,10 +1665,1310 @@
         </is>
       </c>
       <c r="B101">
-        <v>0.3278806193480825</v>
+        <v>0.2098009276385809</v>
       </c>
       <c r="C101">
-        <v>0.9833658354374557</v>
+        <v>-0.1542542138546903</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B102">
+        <v>-0.5713150078562462</v>
+      </c>
+      <c r="C102">
+        <v>0.6286820820656965</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B103">
+        <v>-0.7426419995124175</v>
+      </c>
+      <c r="C103">
+        <v>0.2369535285430048</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="B104">
+        <v>0.05530781756905051</v>
+      </c>
+      <c r="C104">
+        <v>0.5185686796094288</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B105">
+        <v>0.04912128864103576</v>
+      </c>
+      <c r="C105">
+        <v>0.7451267644397518</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B106">
+        <v>1.059899574641835</v>
+      </c>
+      <c r="C106">
+        <v>1.334339870952284</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="B107">
+        <v>1.639143102790869</v>
+      </c>
+      <c r="C107">
+        <v>-0.3963566063091799</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="B108">
+        <v>-1.143662146414995</v>
+      </c>
+      <c r="C108">
+        <v>-0.7933978429907578</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="B109">
+        <v>0.5878003813154294</v>
+      </c>
+      <c r="C109">
+        <v>-2.251434344640972</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="B110">
+        <v>-1.132834046878926</v>
+      </c>
+      <c r="C110">
+        <v>0.6917459788811</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B111">
+        <v>-0.6995504310556377</v>
+      </c>
+      <c r="C111">
+        <v>-1.534625617919958</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="B112">
+        <v>0.322671901771683</v>
+      </c>
+      <c r="C112">
+        <v>0.1524683644987917</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="B113">
+        <v>-0.1940596766768689</v>
+      </c>
+      <c r="C113">
+        <v>0.6205064523822102</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="B114">
+        <v>-0.4827304620891493</v>
+      </c>
+      <c r="C114">
+        <v>0.158430142008495</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="B115">
+        <v>0.02659316532587245</v>
+      </c>
+      <c r="C115">
+        <v>-1.539602301738539</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="B116">
+        <v>-0.2890617901963241</v>
+      </c>
+      <c r="C116">
+        <v>-0.84579349536069</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B117">
+        <v>-0.4743872104659707</v>
+      </c>
+      <c r="C117">
+        <v>0.4306523030330525</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="B118">
+        <v>-0.6915800419168252</v>
+      </c>
+      <c r="C118">
+        <v>-1.273131061640447</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="B119">
+        <v>-0.3576703706775625</v>
+      </c>
+      <c r="C119">
+        <v>0.3543027779944258</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="B120">
+        <v>-0.6830195100595043</v>
+      </c>
+      <c r="C120">
+        <v>0.03409414925531562</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="B121">
+        <v>-0.8834609169245098</v>
+      </c>
+      <c r="C121">
+        <v>0.9167622283994259</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="B122">
+        <v>1.52882225738246</v>
+      </c>
+      <c r="C122">
+        <v>0.6597022012718456</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="B123">
+        <v>1.837377156964144</v>
+      </c>
+      <c r="C123">
+        <v>0.5086217521819865</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="B124">
+        <v>-0.3308941584982071</v>
+      </c>
+      <c r="C124">
+        <v>0.9286034385867021</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="B125">
+        <v>0.3767114750597943</v>
+      </c>
+      <c r="C125">
+        <v>-1.477270768707478</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="B126">
+        <v>-0.9034215442093321</v>
+      </c>
+      <c r="C126">
+        <v>0.1928227212466519</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B127">
+        <v>0.2034119444973669</v>
+      </c>
+      <c r="C127">
+        <v>0.3166241920561581</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="B128">
+        <v>-1.418742915517394</v>
+      </c>
+      <c r="C128">
+        <v>-0.8161904894833658</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="B129">
+        <v>-2.155210816703246</v>
+      </c>
+      <c r="C129">
+        <v>0.507989881101685</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="B130">
+        <v>0.5463838704581353</v>
+      </c>
+      <c r="C130">
+        <v>1.452960862559328</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B131">
+        <v>0.2497790471794352</v>
+      </c>
+      <c r="C131">
+        <v>-0.8713804858366851</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="B132">
+        <v>-0.3678752565558051</v>
+      </c>
+      <c r="C132">
+        <v>0.9204207790133145</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="B133">
+        <v>-0.2795393480967451</v>
+      </c>
+      <c r="C133">
+        <v>1.078450015709072</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="B134">
+        <v>0.92563718050897</v>
+      </c>
+      <c r="C134">
+        <v>0.05274470047539331</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="B135">
+        <v>-0.2902494061500822</v>
+      </c>
+      <c r="C135">
+        <v>0.09631393024560336</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="B136">
+        <v>-1.441132042126429</v>
+      </c>
+      <c r="C136">
+        <v>-1.39885526313185</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="B137">
+        <v>-0.133815852044296</v>
+      </c>
+      <c r="C137">
+        <v>0.3796807478449212</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="B138">
+        <v>0.9898347694555771</v>
+      </c>
+      <c r="C138">
+        <v>1.054839923214621</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="B139">
+        <v>0.4131407401324488</v>
+      </c>
+      <c r="C139">
+        <v>-0.5671771070596812</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="B140">
+        <v>-0.6268224140726708</v>
+      </c>
+      <c r="C140">
+        <v>0.2939345588469178</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B141">
+        <v>-0.4659954665835527</v>
+      </c>
+      <c r="C141">
+        <v>0.5161670330017039</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="B142">
+        <v>1.361666026070526</v>
+      </c>
+      <c r="C142">
+        <v>1.900128180161849</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="B143">
+        <v>-1.807223076410367</v>
+      </c>
+      <c r="C143">
+        <v>-1.427241034741779</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B144">
+        <v>-0.2022452988224933</v>
+      </c>
+      <c r="C144">
+        <v>-0.2227192026269667</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="B145">
+        <v>0.9048868724120265</v>
+      </c>
+      <c r="C145">
+        <v>0.005587701659667266</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="B146">
+        <v>-0.696365050231571</v>
+      </c>
+      <c r="C146">
+        <v>-1.158264088519481</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="B147">
+        <v>1.999126895137069</v>
+      </c>
+      <c r="C147">
+        <v>-0.6351752779094314</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="B148">
+        <v>-0.521987401614688</v>
+      </c>
+      <c r="C148">
+        <v>-2.151784200378677</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="B149">
+        <v>-2.23277567547969</v>
+      </c>
+      <c r="C149">
+        <v>-0.6150471908910959</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="B150">
+        <v>-1.617545526041931</v>
+      </c>
+      <c r="C150">
+        <v>-0.5939699659678866</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="B151">
+        <v>0.7570323708514985</v>
+      </c>
+      <c r="C151">
+        <v>-0.3403318065778688</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="B152">
+        <v>-0.6329721148043751</v>
+      </c>
+      <c r="C152">
+        <v>-0.4822358550615008</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="B153">
+        <v>-0.6531121491133325</v>
+      </c>
+      <c r="C153">
+        <v>-0.4409925269601505</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="B154">
+        <v>-1.161101315988286</v>
+      </c>
+      <c r="C154">
+        <v>0.9350389679448872</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="B155">
+        <v>-0.4222561081980302</v>
+      </c>
+      <c r="C155">
+        <v>0.03547688483919359</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="B156">
+        <v>0.2953515146891371</v>
+      </c>
+      <c r="C156">
+        <v>-0.5453475459492014</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="B157">
+        <v>1.474377708117306</v>
+      </c>
+      <c r="C157">
+        <v>-1.263429089251723</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="B158">
+        <v>1.488841146479414</v>
+      </c>
+      <c r="C158">
+        <v>1.718858235224594</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="B159">
+        <v>-0.7824449849543236</v>
+      </c>
+      <c r="C159">
+        <v>0.7361936557728541</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="B160">
+        <v>0.6032333701852055</v>
+      </c>
+      <c r="C160">
+        <v>0.05359543997656502</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="B161">
+        <v>-0.3852581609165869</v>
+      </c>
+      <c r="C161">
+        <v>-0.3097288844262635</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="B162">
+        <v>-0.06493388273481035</v>
+      </c>
+      <c r="C162">
+        <v>0.4872806828710923</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="B163">
+        <v>0.8878954079188331</v>
+      </c>
+      <c r="C163">
+        <v>0.00911417534615544</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="B164">
+        <v>1.175309763480826</v>
+      </c>
+      <c r="C164">
+        <v>-0.09977881350357498</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="B165">
+        <v>-0.02072474226431512</v>
+      </c>
+      <c r="C165">
+        <v>-0.0387192353464954</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="B166">
+        <v>0.9624445542358524</v>
+      </c>
+      <c r="C166">
+        <v>-0.1931139778511797</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="B167">
+        <v>-1.580624295080158</v>
+      </c>
+      <c r="C167">
+        <v>-1.154745859352972</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="B168">
+        <v>0.2074714613928654</v>
+      </c>
+      <c r="C168">
+        <v>0.4178450699868855</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="B169">
+        <v>0.2223207827511056</v>
+      </c>
+      <c r="C169">
+        <v>-0.0362007493690943</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="B170">
+        <v>-1.461954596696589</v>
+      </c>
+      <c r="C170">
+        <v>0.4449067844144313</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="B171">
+        <v>-0.2845845542190419</v>
+      </c>
+      <c r="C171">
+        <v>-0.8033063466771999</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="B172">
+        <v>0.6769912223727595</v>
+      </c>
+      <c r="C172">
+        <v>1.345183894896203</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="B173">
+        <v>1.089019377332997</v>
+      </c>
+      <c r="C173">
+        <v>0.207490433124997</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="B174">
+        <v>-1.649580676691676</v>
+      </c>
+      <c r="C174">
+        <v>-1.123711959920842</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="B175">
+        <v>1.374474500114415</v>
+      </c>
+      <c r="C175">
+        <v>1.267475978623481</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="B176">
+        <v>-1.172746366533421</v>
+      </c>
+      <c r="C176">
+        <v>-1.254017860195093</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="B177">
+        <v>1.343705083983417</v>
+      </c>
+      <c r="C177">
+        <v>0.3159230806673711</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="B178">
+        <v>-0.5647788718408109</v>
+      </c>
+      <c r="C178">
+        <v>1.067616355248018</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="B179">
+        <v>0.3933499913096006</v>
+      </c>
+      <c r="C179">
+        <v>0.46776972086727</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="B180">
+        <v>0.5416394773839408</v>
+      </c>
+      <c r="C180">
+        <v>-1.123852444346264</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="B181">
+        <v>0.9788146583187665</v>
+      </c>
+      <c r="C181">
+        <v>-0.6259535775407746</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="B182">
+        <v>0.3243193102466688</v>
+      </c>
+      <c r="C182">
+        <v>-0.05510976494730013</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="B183">
+        <v>-1.232859926010434</v>
+      </c>
+      <c r="C183">
+        <v>-0.8455528450821257</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="B184">
+        <v>0.2615619853875591</v>
+      </c>
+      <c r="C184">
+        <v>0.5861359020108716</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="B185">
+        <v>-1.007276351511233</v>
+      </c>
+      <c r="C185">
+        <v>0.7513172410242628</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="B186">
+        <v>-2.019107809151945</v>
+      </c>
+      <c r="C186">
+        <v>0.2794357087989349</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="B187">
+        <v>-0.2448859683038117</v>
+      </c>
+      <c r="C187">
+        <v>-0.07346815027187401</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="B188">
+        <v>0.3601483815989737</v>
+      </c>
+      <c r="C188">
+        <v>0.3588862341065389</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="B189">
+        <v>-1.541068252272946</v>
+      </c>
+      <c r="C189">
+        <v>-1.55537600197453</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="B190">
+        <v>-0.05520401325000403</v>
+      </c>
+      <c r="C190">
+        <v>0.7902274810960582</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="B191">
+        <v>-1.299456202806265</v>
+      </c>
+      <c r="C191">
+        <v>-1.255467229907174</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="B192">
+        <v>-0.4883384753010523</v>
+      </c>
+      <c r="C192">
+        <v>1.658519398506807</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="B193">
+        <v>-0.538056438464801</v>
+      </c>
+      <c r="C193">
+        <v>-0.6958070393157202</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="B194">
+        <v>-0.9259325956742283</v>
+      </c>
+      <c r="C194">
+        <v>0.1444614477500889</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="B195">
+        <v>1.473315649987178</v>
+      </c>
+      <c r="C195">
+        <v>-1.049025197432694</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="B196">
+        <v>1.271294089008877</v>
+      </c>
+      <c r="C196">
+        <v>1.164393374098283</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="B197">
+        <v>-0.564774140100894</v>
+      </c>
+      <c r="C197">
+        <v>-0.4786150605606385</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="B198">
+        <v>-0.2267459638074938</v>
+      </c>
+      <c r="C198">
+        <v>0.2215874921511924</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="B199">
+        <v>0.2393498735811373</v>
+      </c>
+      <c r="C199">
+        <v>-0.645622509663526</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="B200">
+        <v>-0.9576836003588567</v>
+      </c>
+      <c r="C200">
+        <v>-0.947191326433469</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="B201">
+        <v>0.2543910023194692</v>
+      </c>
+      <c r="C201">
+        <v>2.660316408762626</v>
       </c>
     </row>
   </sheetData>
